--- a/tests/realSuite/Piano-Viaggi_Giochiamo-alle-Olimpiadi_21-ottobre-2025_Gardolo/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Giochiamo-alle-Olimpiadi_21-ottobre-2025_Gardolo/input.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,235 +471,280 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Scuola di Bedollo, Via Giacomo Bresadola</t>
+          <t>Scuola Baselga di Pine, via del 26 maggio</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>IC Chiese</t>
+          <t>IC Altopiano di Pinè</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Via Lamarmora, 13 - Borgo Chiese</t>
+          <t>Scuola di Bedollo, Via Giacomo Bresadola</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IC Civezzano</t>
+          <t>IC Chiese</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Scuola di Civezzano, via Telvana 6</t>
+          <t>Via Lamarmora, 13 - Borgo Chiese</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC Folgaria-Lavarone-Luserna</t>
+          <t>IC Civezzano</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Scuola Gionghi di Lavarone</t>
+          <t>Scuola di Civezzano, via Telvana 6</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IC Ladino di Fassa</t>
+          <t>IC Folgaria-Lavarone-Luserna</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hotel Trentino, fermata autobus Via Lowy, 96, 38035, Moena</t>
+          <t>Palaghiaccio Folgaria</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>IC Lavis</t>
+          <t>IC Folgaria-Lavarone-Luserna</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scuola Primaria A. Frank: Piazza SS Filippo e Giacomo 1, Zambana</t>
+          <t>Scuola Gionghi di Lavarone</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IC Mezzano Santa Croce</t>
+          <t>IC Ladino di Fassa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Via Molaren, 29 - Mezzano (TN)</t>
+          <t>Hotel Trentino, fermata autobus Via Lowy, 96, 38035, Moena</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IC Pergine 1</t>
+          <t>IC Lavis</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Via Monte Cristallo, 4 - Pergine Valsugana</t>
+          <t>Scuola Primaria A. Frank: Piazza SS Filippo e Giacomo 1, Zambana</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IC Pergine 2</t>
+          <t>IC Mezzano Santa Croce</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Via delle Nazioni Unite, 44, 38057, Canale, TN</t>
+          <t>Via Molaren, 29 - Mezzano (TN)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>IC Riva 2</t>
+          <t>IC Pergine 1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Via dei laghi, 47 - 38060 Tenno</t>
+          <t>Via Monte Cristallo, 4 - Pergine Valsugana</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>IC Rovereto Est</t>
+          <t>IC Pergine 2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Piazzale Orsi, fermata scuola CFP Veronesi Rovereto</t>
+          <t>Via delle Nazioni Unite, 44, 38057, Canale, TN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IC Taio</t>
+          <t>IC Riva 2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Via delle scuole, Coredo</t>
+          <t>Via dei laghi, 47 - 38060 Tenno</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IC Tione</t>
+          <t>IC Rovereto Est</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Roncone (centro scolastico provvisorio), via Nazionale, 20</t>
+          <t>Piazzale Orsi, fermata scuola CFP Veronesi Rovereto</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IC Val Rendena</t>
+          <t>IC Taio</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Viale della Pace 10 Pinzolo</t>
+          <t>Via delle scuole, Coredo</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>IC Vigolo Vattaro</t>
+          <t>IC Tione</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fermata autocorriere Vigolo Vattaro</t>
+          <t>Ragoli, fermata bus davanti alla Posta in via Trento</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>IC Tione</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Roncone (centro scolastico provvisorio), via Nazionale, 20</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IC Val Rendena</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Viale della Pace 10 Pinzolo</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IC Vigolo Vattaro</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Fermata autocorriere Vigolo Vattaro</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>STUDENTS STAFF – IS GUETTI</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>IS Guetti, Via Durone 53, Tione</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C22" t="n">
         <v>17</v>
       </c>
     </row>

--- a/tests/realSuite/Piano-Viaggi_Giochiamo-alle-Olimpiadi_21-ottobre-2025_Gardolo/input.xlsx
+++ b/tests/realSuite/Piano-Viaggi_Giochiamo-alle-Olimpiadi_21-ottobre-2025_Gardolo/input.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Piazza Condini Romagnano</t>
+          <t>1, Via delle Piazzole, Ravina Romagnano, Romagnano, Trento, Territorio Val d'Adige, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38123, Italia</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -456,7 +456,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Via 25 Aprile, Aldeno</t>
+          <t>Via Venticinque Aprile, Aldeno, Territorio Val d'Adige, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38060, Italia</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Scuola di Bedollo, Via Giacomo Bresadola</t>
+          <t>Via Giacomo Bresadola, Bedol, Centrale, Bedollo, Comunità Alta Valsugana e Bersntol, Provincia di Trento, Trentino-Alto Adige/Südtirol, 38057, Italia</t>
         </is>
       </c>
       <c r="C5" t="n">
